--- a/Output Files/Baselines/baseline_nearestneighbor.xlsx
+++ b/Output Files/Baselines/baseline_nearestneighbor.xlsx
@@ -18163,13 +18163,13 @@
         <v>0.7455555555555554</v>
       </c>
       <c r="H413" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="I413" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J413" t="n">
-        <v>0.6781666666666666</v>
+        <v>0.6803888888888888</v>
       </c>
       <c r="K413" t="n">
         <v>1</v>
@@ -18204,13 +18204,13 @@
         <v>0.7455555555555554</v>
       </c>
       <c r="H414" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="I414" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J414" t="n">
-        <v>0.6781666666666666</v>
+        <v>0.6803888888888888</v>
       </c>
       <c r="K414" t="n">
         <v>2</v>
@@ -18245,13 +18245,13 @@
         <v>0.7455555555555554</v>
       </c>
       <c r="H415" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="I415" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J415" t="n">
-        <v>0.6781666666666666</v>
+        <v>0.6803888888888888</v>
       </c>
       <c r="K415" t="n">
         <v>3</v>
@@ -18409,13 +18409,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H419" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I419" t="n">
         <v>0.33</v>
       </c>
       <c r="J419" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K419" t="n">
         <v>1</v>
@@ -18450,13 +18450,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H420" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I420" t="n">
         <v>0.33</v>
       </c>
       <c r="J420" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K420" t="n">
         <v>2</v>
@@ -18491,13 +18491,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H421" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I421" t="n">
         <v>0.33</v>
       </c>
       <c r="J421" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K421" t="n">
         <v>3</v>
@@ -18532,13 +18532,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H422" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I422" t="n">
         <v>0.33</v>
       </c>
       <c r="J422" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K422" t="n">
         <v>1</v>
@@ -18573,13 +18573,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H423" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I423" t="n">
         <v>0.33</v>
       </c>
       <c r="J423" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K423" t="n">
         <v>2</v>
@@ -18614,13 +18614,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H424" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I424" t="n">
         <v>0.33</v>
       </c>
       <c r="J424" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K424" t="n">
         <v>3</v>
@@ -18655,13 +18655,13 @@
         <v>0.7455555555555554</v>
       </c>
       <c r="H425" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7388888888888888</v>
       </c>
       <c r="I425" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J425" t="n">
-        <v>0.6781666666666666</v>
+        <v>0.6803888888888888</v>
       </c>
       <c r="K425" t="n">
         <v>1</v>
@@ -18696,13 +18696,13 @@
         <v>0.7455555555555554</v>
       </c>
       <c r="H426" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7388888888888888</v>
       </c>
       <c r="I426" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J426" t="n">
-        <v>0.6781666666666666</v>
+        <v>0.6803888888888888</v>
       </c>
       <c r="K426" t="n">
         <v>2</v>
@@ -18737,13 +18737,13 @@
         <v>0.7455555555555554</v>
       </c>
       <c r="H427" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7388888888888888</v>
       </c>
       <c r="I427" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J427" t="n">
-        <v>0.6781666666666666</v>
+        <v>0.6803888888888888</v>
       </c>
       <c r="K427" t="n">
         <v>3</v>
@@ -18901,13 +18901,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H431" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I431" t="n">
         <v>0.33</v>
       </c>
       <c r="J431" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K431" t="n">
         <v>1</v>
@@ -18942,13 +18942,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H432" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I432" t="n">
         <v>0.33</v>
       </c>
       <c r="J432" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K432" t="n">
         <v>2</v>
@@ -18983,13 +18983,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H433" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I433" t="n">
         <v>0.33</v>
       </c>
       <c r="J433" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K433" t="n">
         <v>3</v>
@@ -19024,13 +19024,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H434" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I434" t="n">
         <v>0.33</v>
       </c>
       <c r="J434" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K434" t="n">
         <v>1</v>
@@ -19065,13 +19065,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H435" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I435" t="n">
         <v>0.33</v>
       </c>
       <c r="J435" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K435" t="n">
         <v>2</v>
@@ -19106,13 +19106,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H436" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I436" t="n">
         <v>0.33</v>
       </c>
       <c r="J436" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K436" t="n">
         <v>3</v>
@@ -19147,13 +19147,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H437" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I437" t="n">
         <v>0.33</v>
       </c>
       <c r="J437" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K437" t="n">
         <v>1</v>
@@ -19188,13 +19188,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H438" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I438" t="n">
         <v>0.33</v>
       </c>
       <c r="J438" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K438" t="n">
         <v>2</v>
@@ -19229,13 +19229,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H439" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I439" t="n">
         <v>0.33</v>
       </c>
       <c r="J439" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K439" t="n">
         <v>3</v>
@@ -19270,13 +19270,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H440" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I440" t="n">
         <v>0.33</v>
       </c>
       <c r="J440" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K440" t="n">
         <v>1</v>
@@ -19311,13 +19311,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H441" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I441" t="n">
         <v>0.33</v>
       </c>
       <c r="J441" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K441" t="n">
         <v>2</v>
@@ -19352,13 +19352,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H442" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I442" t="n">
         <v>0.33</v>
       </c>
       <c r="J442" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K442" t="n">
         <v>3</v>
@@ -19393,13 +19393,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H443" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I443" t="n">
         <v>0.33</v>
       </c>
       <c r="J443" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K443" t="n">
         <v>1</v>
@@ -19434,13 +19434,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H444" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I444" t="n">
         <v>0.33</v>
       </c>
       <c r="J444" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K444" t="n">
         <v>2</v>
@@ -19475,13 +19475,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H445" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I445" t="n">
         <v>0.33</v>
       </c>
       <c r="J445" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K445" t="n">
         <v>3</v>
@@ -19762,13 +19762,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H452" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I452" t="n">
         <v>0.33</v>
       </c>
       <c r="J452" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K452" t="n">
         <v>1</v>
@@ -19803,13 +19803,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H453" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I453" t="n">
         <v>0.33</v>
       </c>
       <c r="J453" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K453" t="n">
         <v>2</v>
@@ -19844,13 +19844,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H454" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I454" t="n">
         <v>0.33</v>
       </c>
       <c r="J454" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K454" t="n">
         <v>3</v>
@@ -20131,13 +20131,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H461" t="n">
-        <v>0.7288888888888888</v>
+        <v>0.7399999999999999</v>
       </c>
       <c r="I461" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J461" t="n">
-        <v>0.6793888888888888</v>
+        <v>0.6816111111111111</v>
       </c>
       <c r="K461" t="n">
         <v>1</v>
@@ -20172,13 +20172,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H462" t="n">
-        <v>0.7288888888888888</v>
+        <v>0.7399999999999999</v>
       </c>
       <c r="I462" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J462" t="n">
-        <v>0.6793888888888888</v>
+        <v>0.6816111111111111</v>
       </c>
       <c r="K462" t="n">
         <v>2</v>
@@ -20213,13 +20213,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H463" t="n">
-        <v>0.7288888888888888</v>
+        <v>0.7399999999999999</v>
       </c>
       <c r="I463" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J463" t="n">
-        <v>0.6793888888888888</v>
+        <v>0.6816111111111111</v>
       </c>
       <c r="K463" t="n">
         <v>3</v>
@@ -20377,13 +20377,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H467" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I467" t="n">
         <v>0.33</v>
       </c>
       <c r="J467" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K467" t="n">
         <v>1</v>
@@ -20418,13 +20418,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H468" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I468" t="n">
         <v>0.33</v>
       </c>
       <c r="J468" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K468" t="n">
         <v>2</v>
@@ -20459,13 +20459,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H469" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I469" t="n">
         <v>0.33</v>
       </c>
       <c r="J469" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K469" t="n">
         <v>3</v>
@@ -20500,13 +20500,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H470" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I470" t="n">
         <v>0.33</v>
       </c>
       <c r="J470" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K470" t="n">
         <v>1</v>
@@ -20541,13 +20541,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H471" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I471" t="n">
         <v>0.33</v>
       </c>
       <c r="J471" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K471" t="n">
         <v>2</v>
@@ -20582,13 +20582,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H472" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I472" t="n">
         <v>0.33</v>
       </c>
       <c r="J472" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K472" t="n">
         <v>3</v>
@@ -20869,13 +20869,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H479" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I479" t="n">
         <v>0.33</v>
       </c>
       <c r="J479" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K479" t="n">
         <v>1</v>
@@ -20910,13 +20910,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H480" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I480" t="n">
         <v>0.33</v>
       </c>
       <c r="J480" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K480" t="n">
         <v>2</v>
@@ -20951,13 +20951,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H481" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I481" t="n">
         <v>0.33</v>
       </c>
       <c r="J481" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K481" t="n">
         <v>3</v>
@@ -21238,13 +21238,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H488" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I488" t="n">
         <v>0.33</v>
       </c>
       <c r="J488" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K488" t="n">
         <v>1</v>
@@ -21279,13 +21279,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H489" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I489" t="n">
         <v>0.33</v>
       </c>
       <c r="J489" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K489" t="n">
         <v>2</v>
@@ -21320,13 +21320,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H490" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I490" t="n">
         <v>0.33</v>
       </c>
       <c r="J490" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K490" t="n">
         <v>3</v>
@@ -21361,13 +21361,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H491" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.7244444444444444</v>
       </c>
       <c r="I491" t="n">
         <v>0.33</v>
       </c>
       <c r="J491" t="n">
-        <v>0.6789444444444445</v>
+        <v>0.6811666666666666</v>
       </c>
       <c r="K491" t="n">
         <v>1</v>
@@ -21402,13 +21402,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H492" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.7244444444444444</v>
       </c>
       <c r="I492" t="n">
         <v>0.33</v>
       </c>
       <c r="J492" t="n">
-        <v>0.6789444444444445</v>
+        <v>0.6811666666666666</v>
       </c>
       <c r="K492" t="n">
         <v>2</v>
@@ -21443,13 +21443,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H493" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.7244444444444444</v>
       </c>
       <c r="I493" t="n">
         <v>0.33</v>
       </c>
       <c r="J493" t="n">
-        <v>0.6789444444444445</v>
+        <v>0.6811666666666666</v>
       </c>
       <c r="K493" t="n">
         <v>3</v>
@@ -21730,13 +21730,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H500" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I500" t="n">
         <v>0.33</v>
       </c>
       <c r="J500" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K500" t="n">
         <v>1</v>
@@ -21771,13 +21771,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H501" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I501" t="n">
         <v>0.33</v>
       </c>
       <c r="J501" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K501" t="n">
         <v>2</v>
@@ -21812,13 +21812,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H502" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I502" t="n">
         <v>0.33</v>
       </c>
       <c r="J502" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K502" t="n">
         <v>3</v>
@@ -21976,13 +21976,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H506" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I506" t="n">
         <v>0.33</v>
       </c>
       <c r="J506" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K506" t="n">
         <v>1</v>
@@ -22017,13 +22017,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H507" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I507" t="n">
         <v>0.33</v>
       </c>
       <c r="J507" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K507" t="n">
         <v>2</v>
@@ -22058,13 +22058,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H508" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I508" t="n">
         <v>0.33</v>
       </c>
       <c r="J508" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K508" t="n">
         <v>3</v>
@@ -22099,13 +22099,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H509" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I509" t="n">
         <v>0.33</v>
       </c>
       <c r="J509" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K509" t="n">
         <v>1</v>
@@ -22140,13 +22140,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H510" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I510" t="n">
         <v>0.33</v>
       </c>
       <c r="J510" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K510" t="n">
         <v>2</v>
@@ -22181,13 +22181,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H511" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I511" t="n">
         <v>0.33</v>
       </c>
       <c r="J511" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K511" t="n">
         <v>3</v>
@@ -22222,13 +22222,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H512" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I512" t="n">
         <v>0.33</v>
       </c>
       <c r="J512" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K512" t="n">
         <v>1</v>
@@ -22263,13 +22263,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H513" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I513" t="n">
         <v>0.33</v>
       </c>
       <c r="J513" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K513" t="n">
         <v>2</v>
@@ -22304,13 +22304,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H514" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I514" t="n">
         <v>0.33</v>
       </c>
       <c r="J514" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K514" t="n">
         <v>3</v>
@@ -22345,13 +22345,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H515" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I515" t="n">
         <v>0.33</v>
       </c>
       <c r="J515" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K515" t="n">
         <v>1</v>
@@ -22386,13 +22386,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H516" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I516" t="n">
         <v>0.33</v>
       </c>
       <c r="J516" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K516" t="n">
         <v>2</v>
@@ -22427,13 +22427,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H517" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I517" t="n">
         <v>0.33</v>
       </c>
       <c r="J517" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K517" t="n">
         <v>3</v>
@@ -22468,13 +22468,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H518" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I518" t="n">
         <v>0.33</v>
       </c>
       <c r="J518" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K518" t="n">
         <v>1</v>
@@ -22509,13 +22509,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H519" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I519" t="n">
         <v>0.33</v>
       </c>
       <c r="J519" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K519" t="n">
         <v>2</v>
@@ -22550,13 +22550,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H520" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I520" t="n">
         <v>0.33</v>
       </c>
       <c r="J520" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K520" t="n">
         <v>3</v>
@@ -22591,13 +22591,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H521" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I521" t="n">
         <v>0.33</v>
       </c>
       <c r="J521" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K521" t="n">
         <v>1</v>
@@ -22632,13 +22632,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H522" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I522" t="n">
         <v>0.33</v>
       </c>
       <c r="J522" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K522" t="n">
         <v>2</v>
@@ -22673,13 +22673,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H523" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I523" t="n">
         <v>0.33</v>
       </c>
       <c r="J523" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K523" t="n">
         <v>3</v>
@@ -22714,13 +22714,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H524" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I524" t="n">
         <v>0.33</v>
       </c>
       <c r="J524" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K524" t="n">
         <v>1</v>
@@ -22755,13 +22755,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H525" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I525" t="n">
         <v>0.33</v>
       </c>
       <c r="J525" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K525" t="n">
         <v>2</v>
@@ -22796,13 +22796,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H526" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I526" t="n">
         <v>0.33</v>
       </c>
       <c r="J526" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K526" t="n">
         <v>3</v>
@@ -22837,13 +22837,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H527" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7388888888888888</v>
       </c>
       <c r="I527" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J527" t="n">
-        <v>0.6781666666666666</v>
+        <v>0.6803888888888888</v>
       </c>
       <c r="K527" t="n">
         <v>1</v>
@@ -22878,13 +22878,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H528" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7388888888888888</v>
       </c>
       <c r="I528" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J528" t="n">
-        <v>0.6781666666666666</v>
+        <v>0.6803888888888888</v>
       </c>
       <c r="K528" t="n">
         <v>2</v>
@@ -22919,13 +22919,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H529" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7388888888888888</v>
       </c>
       <c r="I529" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J529" t="n">
-        <v>0.6781666666666666</v>
+        <v>0.6803888888888888</v>
       </c>
       <c r="K529" t="n">
         <v>3</v>
@@ -22960,13 +22960,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H530" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I530" t="n">
         <v>0.33</v>
       </c>
       <c r="J530" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K530" t="n">
         <v>1</v>
@@ -23001,13 +23001,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H531" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I531" t="n">
         <v>0.33</v>
       </c>
       <c r="J531" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K531" t="n">
         <v>2</v>
@@ -23042,13 +23042,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H532" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I532" t="n">
         <v>0.33</v>
       </c>
       <c r="J532" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K532" t="n">
         <v>3</v>
@@ -23083,13 +23083,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H533" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I533" t="n">
         <v>0.33</v>
       </c>
       <c r="J533" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K533" t="n">
         <v>1</v>
@@ -23124,13 +23124,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H534" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I534" t="n">
         <v>0.33</v>
       </c>
       <c r="J534" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K534" t="n">
         <v>2</v>
@@ -23165,13 +23165,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H535" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I535" t="n">
         <v>0.33</v>
       </c>
       <c r="J535" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K535" t="n">
         <v>3</v>
@@ -23329,13 +23329,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H539" t="n">
-        <v>0.7288888888888888</v>
+        <v>0.74</v>
       </c>
       <c r="I539" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J539" t="n">
-        <v>0.6793888888888888</v>
+        <v>0.6816111111111111</v>
       </c>
       <c r="K539" t="n">
         <v>1</v>
@@ -23370,13 +23370,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H540" t="n">
-        <v>0.7288888888888888</v>
+        <v>0.74</v>
       </c>
       <c r="I540" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J540" t="n">
-        <v>0.6793888888888888</v>
+        <v>0.6816111111111111</v>
       </c>
       <c r="K540" t="n">
         <v>2</v>
@@ -23411,13 +23411,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H541" t="n">
-        <v>0.7288888888888888</v>
+        <v>0.74</v>
       </c>
       <c r="I541" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J541" t="n">
-        <v>0.6793888888888888</v>
+        <v>0.6816111111111111</v>
       </c>
       <c r="K541" t="n">
         <v>3</v>
@@ -23452,13 +23452,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H542" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I542" t="n">
         <v>0.33</v>
       </c>
       <c r="J542" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K542" t="n">
         <v>1</v>
@@ -23493,13 +23493,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H543" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I543" t="n">
         <v>0.33</v>
       </c>
       <c r="J543" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K543" t="n">
         <v>2</v>
@@ -23534,13 +23534,13 @@
         <v>0.7488888888888888</v>
       </c>
       <c r="H544" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="I544" t="n">
         <v>0.33</v>
       </c>
       <c r="J544" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K544" t="n">
         <v>3</v>
@@ -23821,13 +23821,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H551" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I551" t="n">
         <v>0.33</v>
       </c>
       <c r="J551" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K551" t="n">
         <v>1</v>
@@ -23862,13 +23862,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H552" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I552" t="n">
         <v>0.33</v>
       </c>
       <c r="J552" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K552" t="n">
         <v>2</v>
@@ -23903,13 +23903,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H553" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I553" t="n">
         <v>0.33</v>
       </c>
       <c r="J553" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K553" t="n">
         <v>3</v>
@@ -24190,13 +24190,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H560" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I560" t="n">
         <v>0.33</v>
       </c>
       <c r="J560" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K560" t="n">
         <v>1</v>
@@ -24231,13 +24231,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H561" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I561" t="n">
         <v>0.33</v>
       </c>
       <c r="J561" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K561" t="n">
         <v>2</v>
@@ -24272,13 +24272,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H562" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666668</v>
       </c>
       <c r="I562" t="n">
         <v>0.33</v>
       </c>
       <c r="J562" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K562" t="n">
         <v>3</v>
@@ -24313,13 +24313,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H563" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I563" t="n">
         <v>0.33</v>
       </c>
       <c r="J563" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K563" t="n">
         <v>1</v>
@@ -24354,13 +24354,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H564" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I564" t="n">
         <v>0.33</v>
       </c>
       <c r="J564" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K564" t="n">
         <v>2</v>
@@ -24395,13 +24395,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H565" t="n">
-        <v>0.7055555555555555</v>
+        <v>0.7166666666666666</v>
       </c>
       <c r="I565" t="n">
         <v>0.33</v>
       </c>
       <c r="J565" t="n">
-        <v>0.6727222222222222</v>
+        <v>0.6749444444444445</v>
       </c>
       <c r="K565" t="n">
         <v>3</v>
@@ -24928,13 +24928,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H578" t="n">
-        <v>0.7122222222222222</v>
+        <v>0.7233333333333333</v>
       </c>
       <c r="I578" t="n">
         <v>0.33</v>
       </c>
       <c r="J578" t="n">
-        <v>0.6777222222222222</v>
+        <v>0.6799444444444445</v>
       </c>
       <c r="K578" t="n">
         <v>1</v>
@@ -24969,13 +24969,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H579" t="n">
-        <v>0.7122222222222222</v>
+        <v>0.7233333333333333</v>
       </c>
       <c r="I579" t="n">
         <v>0.33</v>
       </c>
       <c r="J579" t="n">
-        <v>0.6777222222222222</v>
+        <v>0.6799444444444445</v>
       </c>
       <c r="K579" t="n">
         <v>2</v>
@@ -25010,13 +25010,13 @@
         <v>0.7488888888888889</v>
       </c>
       <c r="H580" t="n">
-        <v>0.7122222222222222</v>
+        <v>0.7233333333333333</v>
       </c>
       <c r="I580" t="n">
         <v>0.33</v>
       </c>
       <c r="J580" t="n">
-        <v>0.6777222222222222</v>
+        <v>0.6799444444444445</v>
       </c>
       <c r="K580" t="n">
         <v>3</v>
@@ -25051,13 +25051,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H581" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7388888888888888</v>
       </c>
       <c r="I581" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J581" t="n">
-        <v>0.6781666666666666</v>
+        <v>0.6803888888888888</v>
       </c>
       <c r="K581" t="n">
         <v>1</v>
@@ -25092,13 +25092,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H582" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7388888888888888</v>
       </c>
       <c r="I582" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J582" t="n">
-        <v>0.6781666666666666</v>
+        <v>0.6803888888888888</v>
       </c>
       <c r="K582" t="n">
         <v>2</v>
@@ -25133,13 +25133,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H583" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7388888888888888</v>
       </c>
       <c r="I583" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J583" t="n">
-        <v>0.6781666666666666</v>
+        <v>0.6803888888888888</v>
       </c>
       <c r="K583" t="n">
         <v>3</v>
@@ -25174,13 +25174,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H584" t="n">
-        <v>0.7288888888888888</v>
+        <v>0.7399999999999999</v>
       </c>
       <c r="I584" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J584" t="n">
-        <v>0.6793888888888888</v>
+        <v>0.6816111111111111</v>
       </c>
       <c r="K584" t="n">
         <v>1</v>
@@ -25215,13 +25215,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H585" t="n">
-        <v>0.7288888888888888</v>
+        <v>0.7399999999999999</v>
       </c>
       <c r="I585" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J585" t="n">
-        <v>0.6793888888888888</v>
+        <v>0.6816111111111111</v>
       </c>
       <c r="K585" t="n">
         <v>2</v>
@@ -25256,13 +25256,13 @@
         <v>0.7455555555555555</v>
       </c>
       <c r="H586" t="n">
-        <v>0.7288888888888888</v>
+        <v>0.7399999999999999</v>
       </c>
       <c r="I586" t="n">
         <v>0.3711111111111111</v>
       </c>
       <c r="J586" t="n">
-        <v>0.6793888888888888</v>
+        <v>0.6816111111111111</v>
       </c>
       <c r="K586" t="n">
         <v>3</v>
